--- a/E/SWAEGA.xlsx
+++ b/E/SWAEGA.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141062</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY CUPID 3X26</t>
+    <t>20116112</t>
+  </si>
+  <si>
+    <t>MAXICORN BBQ 140G</t>
   </si>
   <si>
     <t>SWAEGA</t>
@@ -28,64 +28,40 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10002101</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP MRH140</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20092857</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 130</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20141063</t>
-  </si>
-  <si>
-    <t>SQ CSHW BTRFLY 3X22G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>20139291</t>
+  </si>
+  <si>
+    <t>FLOATY SNACK BWNG 60</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>20116112</t>
-  </si>
-  <si>
-    <t>MAXICORN BBQ 140G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10002101</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP MRH140</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
-  </si>
-  <si>
-    <t>20139291</t>
-  </si>
-  <si>
-    <t>FLOATY SNACK BWNG 60</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
@@ -505,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -572,15 +548,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -589,18 +565,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -609,67 +585,67 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -677,102 +653,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/SWAEGA.xlsx
+++ b/E/SWAEGA.xlsx
@@ -19,7 +19,7 @@
     <t>20116112</t>
   </si>
   <si>
-    <t>MAXICORN BBQ 140G</t>
+    <t>MAXICORN BBQ 130G</t>
   </si>
   <si>
     <t>SWAEGA</t>
